--- a/Assets/asoliddev - Auto Chess/Config/ConstructorConfig.xlsx
+++ b/Assets/asoliddev - Auto Chess/Config/ConstructorConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\project\unity\auto-chess\Assets\asoliddev - Auto Chess\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{825498B6-5011-468A-9376-C363FD2FEA86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02EC8D70-8BCD-417D-AE91-374608DBB644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1" xr2:uid="{01A69C29-627E-4A73-ADC6-9511219C2DBA}"/>
+    <workbookView xWindow="38280" yWindow="-3720" windowWidth="57840" windowHeight="32040" xr2:uid="{01A69C29-627E-4A73-ADC6-9511219C2DBA}"/>
   </bookViews>
   <sheets>
     <sheet name="ConstructorBaseData" sheetId="3" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2006" uniqueCount="862">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2014" uniqueCount="868">
   <si>
     <t>名字</t>
   </si>
@@ -230,10 +230,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>applyDamageMultiple</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>physicalDamage</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1856,32 +1852,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>hitRate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>受击命中率</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>physicalDamageApplyRate</t>
-  </si>
-  <si>
-    <t>fireDamageApplyRate</t>
-  </si>
-  <si>
-    <t>iceDamageApplyRate</t>
-  </si>
-  <si>
-    <t>lightingDamageApplyRate</t>
-  </si>
-  <si>
-    <t>acidDamageApplyRate</t>
-  </si>
-  <si>
-    <t>nonCritChange</t>
-  </si>
-  <si>
     <t>2,27;2,28;2,29</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2576,10 +2550,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>maxArmor + 30,physicalDamageApplyRate * -0.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>maxArmor + 30</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2888,18 +2858,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>hitRate * -0.1,electricPower + 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hitRate * -0.15,electricPower + 2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hitRate * -0.2,electricPower + 5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>electricPower + 8</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2936,18 +2894,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>maxArmor + 50,moveSpeed - 1,fireDamageApplyRate * -0.15,iceDamageApplyRate * -0.15,lightingDamageApplyRate * -0.15,acidDamageApplyRate * -0.15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>maxArmor + 30,moveSpeed - 1,fireDamageApplyRate * -0.1,iceDamageApplyRate * -0.1,lightingDamageApplyRate * -0.1,acidDamageApplyRate * -0.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>maxArmor + 80,moveSpeed - 1,fireDamageApplyRate * -0.2,iceDamageApplyRate * -0.2,lightingDamageApplyRate * -0.2,acidDamageApplyRate * -0.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>physicalDamage + 2,electricPower + 3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3251,6 +3197,75 @@
   <si>
     <t>Icon/ConstructorSlotType/Icon_1</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在装配UI中的偏移</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>offset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{float x, float y, float z}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0,-0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,-0.3,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0.2,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dodgeChange</t>
+  </si>
+  <si>
+    <t>dodgeChange * -0.1,electricPower + 1</t>
+  </si>
+  <si>
+    <t>dodgeChange * -0.15,electricPower + 2</t>
+  </si>
+  <si>
+    <t>dodgeChange * -0.2,electricPower + 5</t>
+  </si>
+  <si>
+    <t>critChange</t>
+  </si>
+  <si>
+    <t>damageDefenceRate</t>
+  </si>
+  <si>
+    <t>physicalDefenceRate</t>
+  </si>
+  <si>
+    <t>fireDefenceRate</t>
+  </si>
+  <si>
+    <t>iceDefenceRate</t>
+  </si>
+  <si>
+    <t>lightingDefenceRate</t>
+  </si>
+  <si>
+    <t>acidDefenceRate</t>
+  </si>
+  <si>
+    <t>maxArmor + 30,moveSpeed - 1,fireDefenceRate * -0.1,iceDefenceRate * -0.1,lightingDefenceRate * -0.1,acidDefenceRate * -0.1</t>
+  </si>
+  <si>
+    <t>maxArmor + 50,moveSpeed - 1,fireDefenceRate * -0.15,iceDefenceRate * -0.15,lightingDefenceRate * -0.15,acidDefenceRate * -0.15</t>
+  </si>
+  <si>
+    <t>maxArmor + 80,moveSpeed - 1,fireDefenceRate * -0.2,iceDefenceRate * -0.2,lightingDefenceRate * -0.2,acidDefenceRate * -0.2</t>
+  </si>
+  <si>
+    <t>maxArmor + 30,physicalDefenceRate * -0.1</t>
   </si>
 </sst>
 </file>
@@ -3778,29 +3793,29 @@
         <v>6</v>
       </c>
       <c r="D1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E1" t="s">
-        <v>738</v>
+        <v>729</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G1" s="24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H1" s="24"/>
       <c r="I1" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>41</v>
       </c>
       <c r="K1" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="L1" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N1" s="25"/>
       <c r="O1" s="25"/>
@@ -3820,31 +3835,31 @@
         <v>7</v>
       </c>
       <c r="D2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" t="s">
+        <v>730</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E2" t="s">
-        <v>739</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>84</v>
-      </c>
       <c r="I2" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>42</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N2" s="25"/>
       <c r="O2" s="25"/>
@@ -3885,10 +3900,10 @@
         <v>15</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L3" s="15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N3" s="25"/>
       <c r="O3" s="25"/>
@@ -3902,13 +3917,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="C4" t="s">
-        <v>783</v>
+        <v>768</v>
       </c>
       <c r="D4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E4" s="17">
         <v>1</v>
@@ -3917,16 +3932,16 @@
         <v>27</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>745</v>
+        <v>736</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>19</v>
@@ -3935,13 +3950,13 @@
         <v>4</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q4" s="1" t="s">
         <v>4</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="S4" s="1" t="s">
         <v>4</v>
@@ -3952,13 +3967,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="C5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E5" s="18">
         <v>2</v>
@@ -3967,16 +3982,16 @@
         <v>27</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>746</v>
+        <v>737</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>28</v>
@@ -3985,16 +4000,16 @@
         <v>20</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="U5" s="1"/>
     </row>
@@ -4003,13 +4018,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="C6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E6" s="17">
         <v>1</v>
@@ -4018,16 +4033,16 @@
         <v>27</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>747</v>
+        <v>738</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>30</v>
@@ -4036,16 +4051,16 @@
         <v>21</v>
       </c>
       <c r="P6" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q6" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="Q6" s="1" t="s">
-        <v>293</v>
-      </c>
       <c r="R6" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
@@ -4055,13 +4070,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="C7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E7" s="18">
         <v>2</v>
@@ -4070,16 +4085,16 @@
         <v>27</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>748</v>
+        <v>739</v>
       </c>
       <c r="K7" s="15" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>31</v>
@@ -4088,16 +4103,16 @@
         <v>22</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
@@ -4107,13 +4122,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C8" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E8" s="19">
         <v>3</v>
@@ -4122,19 +4137,19 @@
         <v>27</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>749</v>
+        <v>740</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>33</v>
@@ -4149,10 +4164,10 @@
         <v>26</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
@@ -4162,13 +4177,13 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C9" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E9" s="17">
         <v>1</v>
@@ -4177,16 +4192,16 @@
         <v>29</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>750</v>
+        <v>741</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>36</v>
@@ -4195,16 +4210,16 @@
         <v>23</v>
       </c>
       <c r="P9" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="Q9" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="Q9" s="1" t="s">
-        <v>287</v>
-      </c>
       <c r="R9" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
@@ -4214,13 +4229,13 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C10" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E10" s="18">
         <v>2</v>
@@ -4229,16 +4244,16 @@
         <v>29</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>751</v>
+        <v>742</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="N10" s="1" t="s">
         <v>37</v>
@@ -4247,16 +4262,16 @@
         <v>25</v>
       </c>
       <c r="P10" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q10" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="Q10" s="1" t="s">
-        <v>290</v>
-      </c>
       <c r="R10" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="V10" s="1"/>
     </row>
@@ -4265,13 +4280,13 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C11" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D11" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E11" s="19">
         <v>3</v>
@@ -4280,19 +4295,19 @@
         <v>29</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>752</v>
+        <v>743</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="N11" s="1" t="s">
         <v>38</v>
@@ -4301,10 +4316,10 @@
         <v>24</v>
       </c>
       <c r="P11" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q11" s="1" t="s">
         <v>295</v>
-      </c>
-      <c r="Q11" s="1" t="s">
-        <v>296</v>
       </c>
       <c r="U11" s="1"/>
       <c r="V11" s="1"/>
@@ -4314,37 +4329,37 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C12" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="D12" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E12" s="17">
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>774</v>
+        <v>762</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P12" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q12" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="Q12" s="1" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
@@ -4352,31 +4367,31 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="C13" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E13" s="18">
         <v>2</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>775</v>
+        <v>763</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="14" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
@@ -4384,31 +4399,31 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="C14" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D14" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E14" s="18">
         <v>2</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>776</v>
+        <v>764</v>
       </c>
       <c r="K14" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="3"/>
@@ -4418,31 +4433,31 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C15" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D15" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E15" s="19">
         <v>3</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>777</v>
+        <v>765</v>
       </c>
       <c r="K15" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="3"/>
@@ -4452,13 +4467,13 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C16" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E16" s="17">
         <v>1</v>
@@ -4467,25 +4482,25 @@
         <v>35</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>753</v>
+        <v>744</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="N16" s="1" t="s">
         <v>43</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="28.5" x14ac:dyDescent="0.2">
@@ -4493,40 +4508,40 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C17" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D17" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E17" s="18">
         <v>2</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>754</v>
+        <v>745</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="N17" s="1" t="s">
         <v>44</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="28.5" x14ac:dyDescent="0.2">
@@ -4534,13 +4549,13 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C18" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D18" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E18" s="19">
         <v>3</v>
@@ -4549,28 +4564,28 @@
         <v>35</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>39</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>755</v>
+        <v>746</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="N18" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="O18" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="O18" s="1" t="s">
-        <v>493</v>
-      </c>
       <c r="Q18" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.2">
@@ -4589,10 +4604,10 @@
         <v>45</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.2">
@@ -4600,13 +4615,13 @@
         <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C20" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E20" s="17">
         <v>1</v>
@@ -4618,22 +4633,22 @@
         <v>39</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>756</v>
+        <v>747</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="N20" s="1" t="s">
         <v>46</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.2">
@@ -4641,13 +4656,13 @@
         <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C21" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E21" s="17">
         <v>1</v>
@@ -4659,22 +4674,22 @@
         <v>39</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="K21" s="15" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="N21" s="1" t="s">
         <v>47</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.2">
@@ -4682,13 +4697,13 @@
         <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C22" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E22" s="18">
         <v>2</v>
@@ -4700,17 +4715,17 @@
         <v>39</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>757</v>
+        <v>748</v>
       </c>
       <c r="K22" s="15" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L22" s="1"/>
       <c r="Q22" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.2">
@@ -4718,13 +4733,13 @@
         <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="C23" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E23" s="17">
         <v>1</v>
@@ -4736,22 +4751,22 @@
         <v>39</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>758</v>
+        <v>749</v>
       </c>
       <c r="K23" s="15" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.2">
@@ -4759,13 +4774,13 @@
         <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="C24" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D24" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E24" s="18">
         <v>2</v>
@@ -4777,22 +4792,22 @@
         <v>39</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>759</v>
+        <v>750</v>
       </c>
       <c r="K24" s="15" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.2">
@@ -4800,13 +4815,13 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C25" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E25" s="18">
         <v>2</v>
@@ -4818,16 +4833,16 @@
         <v>39</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>760</v>
+        <v>751</v>
       </c>
       <c r="K25" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.2">
@@ -4835,13 +4850,13 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C26" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E26" s="19">
         <v>3</v>
@@ -4853,25 +4868,25 @@
         <v>39</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>761</v>
+        <v>752</v>
       </c>
       <c r="K26" s="15" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>506</v>
+        <v>853</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.2">
@@ -4879,13 +4894,13 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C27" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E27" s="19">
         <v>3</v>
@@ -4897,25 +4912,25 @@
         <v>39</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>762</v>
+        <v>753</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>513</v>
+        <v>857</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.2">
@@ -4923,13 +4938,13 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C28" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D28" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E28" s="17">
         <v>1</v>
@@ -4941,22 +4956,22 @@
         <v>39</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>763</v>
+        <v>754</v>
       </c>
       <c r="K28" s="15" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="N28" s="1" t="s">
         <v>48</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>790</v>
+        <v>775</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.2">
@@ -4964,13 +4979,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C29" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D29" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E29" s="18">
         <v>2</v>
@@ -4982,13 +4997,13 @@
         <v>39</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>764</v>
+        <v>755</v>
       </c>
       <c r="K29" s="15" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.2">
@@ -4996,13 +5011,13 @@
         <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="C30" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E30" s="17">
         <v>1</v>
@@ -5014,19 +5029,19 @@
         <v>39</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>766</v>
+        <v>854</v>
       </c>
       <c r="K30" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="N30" s="1" t="s">
         <v>49</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.2">
@@ -5034,13 +5049,13 @@
         <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="C31" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D31" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E31" s="18">
         <v>2</v>
@@ -5052,19 +5067,19 @@
         <v>39</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>767</v>
+        <v>855</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="N31" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="O31" s="1" t="s">
         <v>494</v>
-      </c>
-      <c r="O31" s="1" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.2">
@@ -5072,13 +5087,13 @@
         <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="C32" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D32" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E32" s="19">
         <v>3</v>
@@ -5090,22 +5105,22 @@
         <v>39</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>768</v>
+        <v>856</v>
       </c>
       <c r="K32" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="N32" s="1" t="s">
         <v>50</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.2">
@@ -5113,40 +5128,40 @@
         <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C33" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D33" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E33" s="19">
         <v>3</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>39</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="K33" s="15" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>51</v>
+        <v>858</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.2">
@@ -5154,31 +5169,31 @@
         <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C34" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D34" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E34" s="18">
         <v>2</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>39</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>770</v>
+        <v>758</v>
       </c>
       <c r="K34" s="15" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.2">
@@ -5186,13 +5201,13 @@
         <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C35" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D35" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E35" s="19">
         <v>3</v>
@@ -5204,19 +5219,19 @@
         <v>39</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="K35" s="15" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.2">
@@ -5224,37 +5239,37 @@
         <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C36" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D36" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E36" s="17">
         <v>1</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>39</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="K36" s="15" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.2">
@@ -5262,37 +5277,37 @@
         <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C37" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D37" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E37" s="18">
         <v>2</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>39</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>773</v>
+        <v>761</v>
       </c>
       <c r="K37" s="15" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.2">
@@ -5300,40 +5315,40 @@
         <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C38" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D38" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E38" s="19">
         <v>3</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>39</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>772</v>
+        <v>760</v>
       </c>
       <c r="K38" s="15" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.2">
@@ -5341,37 +5356,37 @@
         <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C39" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D39" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E39" s="17">
         <v>1</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>39</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>771</v>
+        <v>759</v>
       </c>
       <c r="K39" s="15" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.2">
@@ -5392,13 +5407,13 @@
         <v>36</v>
       </c>
       <c r="B41" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="C41" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D41" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E41" s="17">
         <v>1</v>
@@ -5407,19 +5422,19 @@
         <v>32</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>508</v>
+        <v>859</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.2">
@@ -5427,13 +5442,13 @@
         <v>37</v>
       </c>
       <c r="B42" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="C42" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D42" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E42" s="18">
         <v>2</v>
@@ -5442,19 +5457,19 @@
         <v>32</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>509</v>
+        <v>860</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.2">
@@ -5462,13 +5477,13 @@
         <v>38</v>
       </c>
       <c r="B43" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="C43" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D43" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E43" s="17">
         <v>1</v>
@@ -5477,19 +5492,19 @@
         <v>27</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>510</v>
+        <v>861</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.2">
@@ -5497,13 +5512,13 @@
         <v>39</v>
       </c>
       <c r="B44" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="C44" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D44" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E44" s="18">
         <v>2</v>
@@ -5512,19 +5527,19 @@
         <v>27</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>511</v>
+        <v>862</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.2">
@@ -5532,13 +5547,13 @@
         <v>40</v>
       </c>
       <c r="B45" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="C45" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D45" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E45" s="19">
         <v>3</v>
@@ -5547,22 +5562,22 @@
         <v>27</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>512</v>
+        <v>863</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
@@ -5570,13 +5585,13 @@
         <v>44</v>
       </c>
       <c r="B49" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C49" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D49" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E49" s="19">
         <v>3</v>
@@ -5585,19 +5600,19 @@
         <v>32</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="K49" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
@@ -5605,31 +5620,31 @@
         <v>45</v>
       </c>
       <c r="B50" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="C50" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D50" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E50" s="18">
         <v>2</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="K50" s="15" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
@@ -5637,34 +5652,34 @@
         <v>46</v>
       </c>
       <c r="B51" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="C51" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D51" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E51" s="19">
         <v>3</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>39</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="K51" s="15" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
@@ -5672,28 +5687,28 @@
         <v>47</v>
       </c>
       <c r="B52" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C52" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D52" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E52" s="17">
         <v>1</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
@@ -5701,13 +5716,13 @@
         <v>48</v>
       </c>
       <c r="B53" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C53" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D53" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E53" s="17">
         <v>1</v>
@@ -5716,16 +5731,16 @@
         <v>35</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="K53" s="15" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.2">
@@ -5733,13 +5748,13 @@
         <v>49</v>
       </c>
       <c r="B54" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C54" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D54" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E54" s="18">
         <v>2</v>
@@ -5748,16 +5763,16 @@
         <v>35</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="K54" s="15" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.2">
@@ -5765,13 +5780,13 @@
         <v>50</v>
       </c>
       <c r="B55" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C55" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D55" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E55" s="19">
         <v>3</v>
@@ -5780,16 +5795,16 @@
         <v>35</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.2">
@@ -5797,28 +5812,28 @@
         <v>51</v>
       </c>
       <c r="B56" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C56" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D56" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E56" s="17">
         <v>1</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
@@ -5826,31 +5841,31 @@
         <v>52</v>
       </c>
       <c r="B57" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C57" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D57" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E57" s="19">
         <v>3</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.2">
@@ -5858,28 +5873,28 @@
         <v>53</v>
       </c>
       <c r="B58" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C58" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D58" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E58" s="18">
         <v>2</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.2">
@@ -5887,13 +5902,13 @@
         <v>57</v>
       </c>
       <c r="B62" t="s">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="C62" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D62" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E62" s="17">
         <v>1</v>
@@ -5902,16 +5917,16 @@
         <v>29</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="K62" s="15" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.2">
@@ -5919,13 +5934,13 @@
         <v>58</v>
       </c>
       <c r="B63" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="C63" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D63" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E63" s="18">
         <v>2</v>
@@ -5934,16 +5949,16 @@
         <v>29</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="K63" s="15" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.2">
@@ -5951,13 +5966,13 @@
         <v>59</v>
       </c>
       <c r="B64" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="C64" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D64" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E64" s="19">
         <v>3</v>
@@ -5966,19 +5981,19 @@
         <v>29</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="K64" s="15" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.2">
@@ -5999,13 +6014,13 @@
         <v>60</v>
       </c>
       <c r="B66" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="C66" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D66" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E66" s="19">
         <v>3</v>
@@ -6014,13 +6029,13 @@
         <v>27</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="K66" s="15" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.2">
@@ -6028,13 +6043,13 @@
         <v>61</v>
       </c>
       <c r="B67" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="C67" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D67" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E67" s="19">
         <v>3</v>
@@ -6043,13 +6058,13 @@
         <v>29</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="K67" s="15" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
@@ -6057,13 +6072,13 @@
         <v>62</v>
       </c>
       <c r="B68" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="C68" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D68" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E68" s="19">
         <v>3</v>
@@ -6072,13 +6087,13 @@
         <v>27</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="K68" s="15" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
@@ -6086,13 +6101,13 @@
         <v>63</v>
       </c>
       <c r="B69" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="C69" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D69" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E69" s="19">
         <v>3</v>
@@ -6101,13 +6116,13 @@
         <v>29</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="K69" s="15" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.2">
@@ -6115,13 +6130,13 @@
         <v>64</v>
       </c>
       <c r="B70" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="C70" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D70" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E70" s="19">
         <v>3</v>
@@ -6130,13 +6145,13 @@
         <v>35</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="K70" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.2">
@@ -6144,13 +6159,13 @@
         <v>65</v>
       </c>
       <c r="B71" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="C71" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D71" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E71" s="19">
         <v>3</v>
@@ -6159,13 +6174,13 @@
         <v>35</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="K71" s="15" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.2">
@@ -6186,13 +6201,13 @@
         <v>66</v>
       </c>
       <c r="B73" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="C73" t="s">
-        <v>692</v>
+        <v>683</v>
       </c>
       <c r="D73" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E73" s="17">
         <v>1</v>
@@ -6201,16 +6216,16 @@
         <v>32</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K73" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L73" s="15" t="s">
-        <v>700</v>
+        <v>691</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.2">
@@ -6218,13 +6233,13 @@
         <v>67</v>
       </c>
       <c r="B74" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="C74" t="s">
-        <v>693</v>
+        <v>684</v>
       </c>
       <c r="D74" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E74" s="18">
         <v>2</v>
@@ -6233,19 +6248,19 @@
         <v>32</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="K74" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L74" s="15" t="s">
-        <v>701</v>
+        <v>692</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
@@ -6253,13 +6268,13 @@
         <v>68</v>
       </c>
       <c r="B75" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="C75" t="s">
-        <v>694</v>
+        <v>685</v>
       </c>
       <c r="D75" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E75" s="19">
         <v>3</v>
@@ -6268,19 +6283,19 @@
         <v>32</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="K75" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L75" s="15" t="s">
-        <v>702</v>
+        <v>693</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.2">
@@ -6288,13 +6303,13 @@
         <v>69</v>
       </c>
       <c r="B76" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C76" t="s">
-        <v>695</v>
+        <v>686</v>
       </c>
       <c r="D76" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E76" s="17">
         <v>1</v>
@@ -6303,13 +6318,13 @@
         <v>29</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K76" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.2">
@@ -6317,13 +6332,13 @@
         <v>70</v>
       </c>
       <c r="B77" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C77" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D77" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E77" s="18">
         <v>2</v>
@@ -6332,16 +6347,16 @@
         <v>29</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="K77" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.2">
@@ -6349,13 +6364,13 @@
         <v>71</v>
       </c>
       <c r="B78" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C78" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D78" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E78" s="19">
         <v>3</v>
@@ -6364,16 +6379,16 @@
         <v>29</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="K78" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
@@ -6381,31 +6396,31 @@
         <v>72</v>
       </c>
       <c r="B79" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="C79" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D79" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E79" s="17">
         <v>1</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K79" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.2">
@@ -6413,34 +6428,34 @@
         <v>73</v>
       </c>
       <c r="B80" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="C80" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D80" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E80" s="18">
         <v>2</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="K80" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.2">
@@ -6448,34 +6463,34 @@
         <v>74</v>
       </c>
       <c r="B81" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="C81" t="s">
-        <v>696</v>
+        <v>687</v>
       </c>
       <c r="D81" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E81" s="19">
         <v>3</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>703</v>
+        <v>694</v>
       </c>
       <c r="K81" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.2">
@@ -6496,28 +6511,28 @@
         <v>75</v>
       </c>
       <c r="B83" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="C83" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D83" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E83" s="17">
         <v>1</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.2">
@@ -6525,28 +6540,28 @@
         <v>76</v>
       </c>
       <c r="B84" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="C84" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D84" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E84" s="18">
         <v>2</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.2">
@@ -6554,31 +6569,31 @@
         <v>77</v>
       </c>
       <c r="B85" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="C85" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D85" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E85" s="19">
         <v>3</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.2">
@@ -6586,13 +6601,13 @@
         <v>78</v>
       </c>
       <c r="B86" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="C86" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D86" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E86" s="17">
         <v>1</v>
@@ -6601,16 +6616,16 @@
         <v>27</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J86" s="4" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="K86" s="15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.2">
@@ -6618,13 +6633,13 @@
         <v>79</v>
       </c>
       <c r="B87" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="C87" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D87" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E87" s="18">
         <v>2</v>
@@ -6633,16 +6648,16 @@
         <v>27</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="K87" s="15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.2">
@@ -6650,13 +6665,13 @@
         <v>80</v>
       </c>
       <c r="B88" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="C88" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D88" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E88" s="19">
         <v>3</v>
@@ -6665,19 +6680,19 @@
         <v>27</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J88" s="4" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="K88" s="15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.2">
@@ -6685,31 +6700,31 @@
         <v>81</v>
       </c>
       <c r="B89" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="C89" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D89" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E89" s="17">
         <v>1</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="K89" s="15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.2">
@@ -6717,31 +6732,31 @@
         <v>82</v>
       </c>
       <c r="B90" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="C90" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D90" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E90" s="18">
         <v>2</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J90" s="4" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="K90" s="15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.2">
@@ -6749,34 +6764,34 @@
         <v>83</v>
       </c>
       <c r="B91" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="C91" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D91" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E91" s="19">
         <v>3</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J91" s="4" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="K91" s="15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.2">
@@ -6784,13 +6799,13 @@
         <v>84</v>
       </c>
       <c r="B92" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="C92" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D92" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E92" s="18">
         <v>2</v>
@@ -6799,16 +6814,16 @@
         <v>29</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J92" s="4" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="K92" s="15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.2">
@@ -6816,31 +6831,31 @@
         <v>85</v>
       </c>
       <c r="B93" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="C93" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D93" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E93" s="17">
         <v>1</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J93" s="4" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="K93" s="15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.2">
@@ -6848,13 +6863,13 @@
         <v>86</v>
       </c>
       <c r="B94" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="C94" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D94" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E94" s="17">
         <v>1</v>
@@ -6863,16 +6878,16 @@
         <v>29</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="K94" s="15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.2">
@@ -6880,13 +6895,13 @@
         <v>87</v>
       </c>
       <c r="B95" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="C95" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D95" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E95" s="18">
         <v>2</v>
@@ -6895,16 +6910,16 @@
         <v>29</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J95" s="4" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="K95" s="15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.2">
@@ -6912,13 +6927,13 @@
         <v>88</v>
       </c>
       <c r="B96" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="C96" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D96" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E96" s="18">
         <v>2</v>
@@ -6927,16 +6942,16 @@
         <v>29</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J96" s="4" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="K96" s="15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.2">
@@ -6944,13 +6959,13 @@
         <v>89</v>
       </c>
       <c r="B97" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="C97" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D97" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E97" s="18">
         <v>2</v>
@@ -6959,16 +6974,16 @@
         <v>29</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J97" s="4" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="K97" s="15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.2">
@@ -6976,13 +6991,13 @@
         <v>90</v>
       </c>
       <c r="B98" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="C98" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D98" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E98" s="18">
         <v>2</v>
@@ -6994,13 +7009,13 @@
         <v>39</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J98" s="4" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="K98" s="15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.2">
@@ -7008,13 +7023,13 @@
         <v>91</v>
       </c>
       <c r="B99" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="C99" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D99" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E99" s="17">
         <v>1</v>
@@ -7026,13 +7041,13 @@
         <v>39</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J99" s="4" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="K99" s="15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.2">
@@ -7040,13 +7055,13 @@
         <v>92</v>
       </c>
       <c r="B100" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="C100" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D100" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E100" s="19">
         <v>3</v>
@@ -7058,16 +7073,16 @@
         <v>39</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J100" s="4" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="K100" s="15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.2">
@@ -7075,13 +7090,13 @@
         <v>93</v>
       </c>
       <c r="B101" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="C101" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="D101" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E101" s="17">
         <v>1</v>
@@ -7090,16 +7105,16 @@
         <v>32</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J101" s="4" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="K101" s="15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.2">
@@ -7107,13 +7122,13 @@
         <v>94</v>
       </c>
       <c r="B102" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="C102" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D102" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E102" s="18">
         <v>2</v>
@@ -7122,16 +7137,16 @@
         <v>32</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J102" s="4" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="K102" s="15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.2">
@@ -7139,13 +7154,13 @@
         <v>95</v>
       </c>
       <c r="B103" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="C103" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D103" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E103" s="19">
         <v>3</v>
@@ -7154,19 +7169,19 @@
         <v>32</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J103" s="4" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="K103" s="15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.2">
@@ -7174,13 +7189,13 @@
         <v>96</v>
       </c>
       <c r="B104" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="C104" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D104" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E104" s="17">
         <v>1</v>
@@ -7189,16 +7204,16 @@
         <v>32</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J104" s="4" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="K104" s="15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.2">
@@ -7206,13 +7221,13 @@
         <v>97</v>
       </c>
       <c r="B105" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="C105" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D105" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E105" s="18">
         <v>2</v>
@@ -7221,16 +7236,16 @@
         <v>32</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J105" s="4" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="K105" s="15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.2">
@@ -7238,13 +7253,13 @@
         <v>98</v>
       </c>
       <c r="B106" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="C106" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D106" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E106" s="19">
         <v>3</v>
@@ -7253,19 +7268,19 @@
         <v>32</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J106" s="4" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="K106" s="15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.2">
@@ -7286,31 +7301,31 @@
         <v>99</v>
       </c>
       <c r="B108" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="C108" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D108" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E108" s="17">
         <v>1</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J108" s="4" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="K108" s="15" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.2">
@@ -7318,31 +7333,31 @@
         <v>100</v>
       </c>
       <c r="B109" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="C109" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D109" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E109" s="18">
         <v>2</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J109" s="4" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="K109" s="15" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.2">
@@ -7350,34 +7365,34 @@
         <v>101</v>
       </c>
       <c r="B110" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="C110" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D110" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E110" s="19">
         <v>3</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J110" s="4" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="K110" s="15" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.2">
@@ -7385,13 +7400,13 @@
         <v>102</v>
       </c>
       <c r="B111" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="C111" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D111" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E111" s="17">
         <v>1</v>
@@ -7400,16 +7415,16 @@
         <v>27</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J111" s="4" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="K111" s="15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.2">
@@ -7417,13 +7432,13 @@
         <v>103</v>
       </c>
       <c r="B112" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="C112" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D112" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E112" s="18">
         <v>2</v>
@@ -7432,16 +7447,16 @@
         <v>27</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J112" s="4" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="K112" s="15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.2">
@@ -7449,13 +7464,13 @@
         <v>104</v>
       </c>
       <c r="B113" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="C113" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D113" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E113" s="19">
         <v>3</v>
@@ -7464,19 +7479,19 @@
         <v>27</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J113" s="4" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="K113" s="15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.2">
@@ -7484,13 +7499,13 @@
         <v>105</v>
       </c>
       <c r="B114" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="C114" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D114" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E114" s="18">
         <v>2</v>
@@ -7499,16 +7514,16 @@
         <v>29</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J114" s="4" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="K114" s="15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.2">
@@ -7516,13 +7531,13 @@
         <v>106</v>
       </c>
       <c r="B115" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="C115" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D115" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E115" s="17">
         <v>1</v>
@@ -7531,16 +7546,16 @@
         <v>29</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J115" s="4" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="K115" s="15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.2">
@@ -7548,31 +7563,31 @@
         <v>107</v>
       </c>
       <c r="B116" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="C116" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D116" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E116" s="18">
         <v>2</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J116" s="4" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="K116" s="15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.2">
@@ -7580,34 +7595,34 @@
         <v>108</v>
       </c>
       <c r="B117" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="C117" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D117" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E117" s="19">
         <v>3</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J117" s="4" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="K117" s="15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.2">
@@ -7615,13 +7630,13 @@
         <v>109</v>
       </c>
       <c r="B118" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="C118" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D118" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E118" s="19">
         <v>3</v>
@@ -7633,16 +7648,16 @@
         <v>39</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J118" s="4" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="K118" s="15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.2">
@@ -7650,13 +7665,13 @@
         <v>110</v>
       </c>
       <c r="B119" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="C119" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D119" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E119" s="18">
         <v>2</v>
@@ -7665,16 +7680,16 @@
         <v>29</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J119" s="4" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="K119" s="15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.2">
@@ -7682,13 +7697,13 @@
         <v>111</v>
       </c>
       <c r="B120" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="C120" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D120" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E120" s="18">
         <v>2</v>
@@ -7697,16 +7712,16 @@
         <v>29</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J120" s="4" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="K120" s="15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.2">
@@ -7714,13 +7729,13 @@
         <v>112</v>
       </c>
       <c r="B121" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="C121" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D121" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E121" s="18">
         <v>2</v>
@@ -7729,16 +7744,16 @@
         <v>29</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J121" s="4" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="K121" s="15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.2">
@@ -7746,13 +7761,13 @@
         <v>113</v>
       </c>
       <c r="B122" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="C122" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D122" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E122" s="18">
         <v>2</v>
@@ -7764,13 +7779,13 @@
         <v>39</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J122" s="4" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="K122" s="15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.2">
@@ -7778,13 +7793,13 @@
         <v>114</v>
       </c>
       <c r="B123" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="C123" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D123" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E123" s="17">
         <v>1</v>
@@ -7796,13 +7811,13 @@
         <v>39</v>
       </c>
       <c r="I123" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J123" s="4" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="K123" s="15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.2">
@@ -7823,13 +7838,13 @@
         <v>115</v>
       </c>
       <c r="B125" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="C125" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D125" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E125" s="17">
         <v>1</v>
@@ -7838,16 +7853,16 @@
         <v>27</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J125" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K125" s="15" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.2">
@@ -7855,13 +7870,13 @@
         <v>116</v>
       </c>
       <c r="B126" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="C126" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D126" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E126" s="18">
         <v>2</v>
@@ -7870,16 +7885,16 @@
         <v>27</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J126" s="4" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="K126" s="15" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.2">
@@ -7887,13 +7902,13 @@
         <v>117</v>
       </c>
       <c r="B127" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="C127" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D127" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E127" s="19">
         <v>3</v>
@@ -7902,19 +7917,19 @@
         <v>27</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J127" s="4" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="K127" s="15" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.2">
@@ -7922,13 +7937,13 @@
         <v>118</v>
       </c>
       <c r="B128" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="C128" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D128" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E128" s="17">
         <v>1</v>
@@ -7937,16 +7952,16 @@
         <v>35</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J128" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K128" s="15" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.2">
@@ -7954,13 +7969,13 @@
         <v>119</v>
       </c>
       <c r="B129" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="C129" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D129" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E129" s="18">
         <v>2</v>
@@ -7969,16 +7984,16 @@
         <v>35</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J129" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K129" s="15" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.2">
@@ -7986,13 +8001,13 @@
         <v>120</v>
       </c>
       <c r="B130" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="C130" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D130" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E130" s="19">
         <v>3</v>
@@ -8001,19 +8016,19 @@
         <v>35</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J130" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K130" s="15" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.2">
@@ -8034,13 +8049,13 @@
         <v>121</v>
       </c>
       <c r="B132" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="C132" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="D132" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E132" s="17">
         <v>1</v>
@@ -8049,10 +8064,10 @@
         <v>35</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I132" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.2">
@@ -8060,13 +8075,13 @@
         <v>122</v>
       </c>
       <c r="B133" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="C133" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="D133" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E133" s="17">
         <v>1</v>
@@ -8075,16 +8090,16 @@
         <v>32</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J133" s="4" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="L133" s="15" t="s">
-        <v>704</v>
+        <v>695</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.2">
@@ -8092,13 +8107,13 @@
         <v>123</v>
       </c>
       <c r="B134" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="C134" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="D134" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E134" s="17">
         <v>1</v>
@@ -8107,16 +8122,16 @@
         <v>27</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I134" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J134" s="4" t="s">
-        <v>781</v>
+        <v>766</v>
       </c>
       <c r="L134" s="15" t="s">
-        <v>836</v>
+        <v>821</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.2">
@@ -8124,13 +8139,13 @@
         <v>124</v>
       </c>
       <c r="B135" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="C135" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="D135" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E135" s="18">
         <v>2</v>
@@ -8139,13 +8154,13 @@
         <v>32</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I135" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J135" s="4" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="L135" s="15">
         <v>11</v>
@@ -8156,13 +8171,13 @@
         <v>125</v>
       </c>
       <c r="B136" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="C136" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="D136" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E136" s="18">
         <v>2</v>
@@ -8171,13 +8186,13 @@
         <v>32</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I136" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J136" s="4" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.2">
@@ -8185,13 +8200,13 @@
         <v>126</v>
       </c>
       <c r="B137" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="C137" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D137" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E137" s="17">
         <v>1</v>
@@ -8200,10 +8215,10 @@
         <v>32</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I137" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.2">
@@ -8211,13 +8226,13 @@
         <v>127</v>
       </c>
       <c r="B138" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="C138" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D138" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E138" s="18">
         <v>2</v>
@@ -8226,13 +8241,13 @@
         <v>32</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I138" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J138" s="4" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.2">
@@ -8240,13 +8255,13 @@
         <v>128</v>
       </c>
       <c r="B139" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="C139" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D139" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E139" s="19">
         <v>3</v>
@@ -8255,16 +8270,16 @@
         <v>32</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I139" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J139" s="4" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.2">
@@ -8272,28 +8287,28 @@
         <v>129</v>
       </c>
       <c r="B140" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="C140" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="D140" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E140" s="18">
         <v>2</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I140" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J140" s="4" t="s">
-        <v>705</v>
+        <v>696</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.2">
@@ -8301,13 +8316,13 @@
         <v>130</v>
       </c>
       <c r="B141" t="s">
-        <v>742</v>
+        <v>733</v>
       </c>
       <c r="C141" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D141" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E141" s="17">
         <v>1</v>
@@ -8316,10 +8331,10 @@
         <v>32</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I141" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L141" s="1"/>
     </row>
@@ -8328,13 +8343,13 @@
         <v>131</v>
       </c>
       <c r="B142" t="s">
-        <v>743</v>
+        <v>734</v>
       </c>
       <c r="C142" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D142" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E142" s="18">
         <v>2</v>
@@ -8343,13 +8358,13 @@
         <v>32</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I142" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J142" s="4" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="L142" s="1"/>
     </row>
@@ -8358,13 +8373,13 @@
         <v>132</v>
       </c>
       <c r="B143" t="s">
-        <v>744</v>
+        <v>735</v>
       </c>
       <c r="C143" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D143" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E143" s="19">
         <v>3</v>
@@ -8373,16 +8388,16 @@
         <v>32</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I143" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J143" s="4" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="L143" s="1"/>
     </row>
@@ -8404,13 +8419,13 @@
         <v>133</v>
       </c>
       <c r="B145" t="s">
-        <v>706</v>
+        <v>697</v>
       </c>
       <c r="C145" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D145" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E145" s="17">
         <v>1</v>
@@ -8419,10 +8434,10 @@
         <v>32</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.2">
@@ -8430,13 +8445,13 @@
         <v>134</v>
       </c>
       <c r="B146" t="s">
-        <v>707</v>
+        <v>698</v>
       </c>
       <c r="C146" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D146" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E146" s="18">
         <v>2</v>
@@ -8445,13 +8460,13 @@
         <v>32</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I146" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J146" s="4" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.2">
@@ -8459,13 +8474,13 @@
         <v>135</v>
       </c>
       <c r="B147" t="s">
-        <v>708</v>
+        <v>699</v>
       </c>
       <c r="C147" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D147" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E147" s="19">
         <v>3</v>
@@ -8474,16 +8489,16 @@
         <v>32</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I147" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J147" s="4" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.2">
@@ -8491,13 +8506,13 @@
         <v>136</v>
       </c>
       <c r="B148" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="C148" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D148" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E148" s="17">
         <v>1</v>
@@ -8506,10 +8521,10 @@
         <v>32</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I148" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.2">
@@ -8517,13 +8532,13 @@
         <v>137</v>
       </c>
       <c r="B149" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="C149" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D149" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E149" s="18">
         <v>2</v>
@@ -8532,10 +8547,10 @@
         <v>32</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.2">
@@ -8543,13 +8558,13 @@
         <v>138</v>
       </c>
       <c r="B150" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="C150" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D150" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E150" s="19">
         <v>3</v>
@@ -8558,13 +8573,13 @@
         <v>32</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H150" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.2">
@@ -8572,13 +8587,13 @@
         <v>139</v>
       </c>
       <c r="B151" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="C151" t="s">
-        <v>697</v>
+        <v>688</v>
       </c>
       <c r="D151" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E151" s="17">
         <v>1</v>
@@ -8587,13 +8602,13 @@
         <v>32</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I151" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J151" s="4" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.2">
@@ -8601,13 +8616,13 @@
         <v>140</v>
       </c>
       <c r="B152" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="C152" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D152" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E152" s="18">
         <v>2</v>
@@ -8616,13 +8631,13 @@
         <v>32</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I152" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J152" s="4" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.2">
@@ -8630,13 +8645,13 @@
         <v>141</v>
       </c>
       <c r="B153" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="C153" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D153" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E153" s="19">
         <v>3</v>
@@ -8645,13 +8660,13 @@
         <v>32</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I153" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J153" s="4" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.2">
@@ -8659,13 +8674,13 @@
         <v>142</v>
       </c>
       <c r="B154" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="C154" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D154" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E154" s="20">
         <v>4</v>
@@ -8674,13 +8689,13 @@
         <v>32</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I154" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J154" s="4" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.2">
@@ -8688,13 +8703,13 @@
         <v>143</v>
       </c>
       <c r="B155" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="C155" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D155" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E155" s="21">
         <v>5</v>
@@ -8703,16 +8718,16 @@
         <v>32</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H155" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I155" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J155" s="4" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.2">
@@ -8720,13 +8735,13 @@
         <v>144</v>
       </c>
       <c r="B156" t="s">
-        <v>709</v>
+        <v>700</v>
       </c>
       <c r="C156" t="s">
-        <v>698</v>
+        <v>689</v>
       </c>
       <c r="D156" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E156" s="17">
         <v>1</v>
@@ -8735,10 +8750,10 @@
         <v>32</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I156" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.2">
@@ -8746,13 +8761,13 @@
         <v>145</v>
       </c>
       <c r="B157" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="C157" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D157" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E157" s="18">
         <v>2</v>
@@ -8761,13 +8776,13 @@
         <v>32</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I157" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J157" s="4" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.2">
@@ -8775,13 +8790,13 @@
         <v>146</v>
       </c>
       <c r="B158" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="C158" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D158" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E158" s="19">
         <v>3</v>
@@ -8790,16 +8805,16 @@
         <v>32</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I158" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J158" s="4" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.2">
@@ -8807,25 +8822,25 @@
         <v>147</v>
       </c>
       <c r="B159" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="C159" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D159" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E159" s="17">
         <v>1</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I159" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.2">
@@ -8833,28 +8848,28 @@
         <v>148</v>
       </c>
       <c r="B160" t="s">
-        <v>711</v>
+        <v>702</v>
       </c>
       <c r="C160" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D160" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E160" s="18">
         <v>2</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I160" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J160" s="4" t="s">
-        <v>714</v>
+        <v>705</v>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.2">
@@ -8862,31 +8877,31 @@
         <v>149</v>
       </c>
       <c r="B161" t="s">
-        <v>712</v>
+        <v>703</v>
       </c>
       <c r="C161" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D161" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E161" s="19">
         <v>3</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H161" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I161" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J161" s="4" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.2">
@@ -8894,28 +8909,28 @@
         <v>150</v>
       </c>
       <c r="B162" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="C162" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D162" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E162" s="17">
         <v>1</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I162" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J162" s="4" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.2">
@@ -8923,28 +8938,28 @@
         <v>151</v>
       </c>
       <c r="B163" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="C163" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D163" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E163" s="18">
         <v>2</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I163" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J163" s="4" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.2">
@@ -8952,31 +8967,31 @@
         <v>152</v>
       </c>
       <c r="B164" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="C164" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D164" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E164" s="19">
         <v>3</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I164" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J164" s="4" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.2">
@@ -8984,25 +8999,25 @@
         <v>153</v>
       </c>
       <c r="B165" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="C165" t="s">
-        <v>699</v>
+        <v>690</v>
       </c>
       <c r="D165" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E165" s="17">
         <v>1</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I165" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.2">
@@ -9010,28 +9025,28 @@
         <v>154</v>
       </c>
       <c r="B166" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="C166" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D166" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E166" s="18">
         <v>2</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I166" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J166" s="4" t="s">
-        <v>715</v>
+        <v>706</v>
       </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.2">
@@ -9039,28 +9054,28 @@
         <v>155</v>
       </c>
       <c r="B167" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="C167" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D167" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E167" s="19">
         <v>3</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J167" s="4" t="s">
-        <v>716</v>
+        <v>707</v>
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.2">
@@ -9068,28 +9083,28 @@
         <v>156</v>
       </c>
       <c r="B168" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="C168" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D168" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E168" s="20">
         <v>4</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I168" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J168" s="4" t="s">
-        <v>717</v>
+        <v>708</v>
       </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.2">
@@ -9097,13 +9112,13 @@
         <v>157</v>
       </c>
       <c r="B169" t="s">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="C169" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D169" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E169" s="21">
         <v>5</v>
@@ -9112,19 +9127,19 @@
         <v>31</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I169" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J169" s="4" t="s">
-        <v>718</v>
+        <v>709</v>
       </c>
       <c r="K169" s="15" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.2">
@@ -9132,28 +9147,28 @@
         <v>158</v>
       </c>
       <c r="B170" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="C170" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D170" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E170" s="17">
         <v>1</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I170" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J170" s="4" t="s">
-        <v>719</v>
+        <v>710</v>
       </c>
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.2">
@@ -9161,28 +9176,28 @@
         <v>159</v>
       </c>
       <c r="B171" t="s">
-        <v>653</v>
+        <v>645</v>
       </c>
       <c r="C171" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D171" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E171" s="18">
         <v>2</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I171" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J171" s="4" t="s">
-        <v>714</v>
+        <v>705</v>
       </c>
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.2">
@@ -9190,28 +9205,28 @@
         <v>160</v>
       </c>
       <c r="B172" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
       <c r="C172" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D172" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E172" s="19">
         <v>3</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I172" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J172" s="4" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.2">
@@ -9219,28 +9234,28 @@
         <v>161</v>
       </c>
       <c r="B173" t="s">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="C173" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D173" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E173" s="20">
         <v>4</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J173" s="4" t="s">
-        <v>720</v>
+        <v>711</v>
       </c>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.2">
@@ -9248,31 +9263,31 @@
         <v>162</v>
       </c>
       <c r="B174" t="s">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="C174" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D174" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E174" s="21">
         <v>5</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H174" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I174" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J174" s="4" t="s">
-        <v>721</v>
+        <v>712</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.2">
@@ -9280,13 +9295,13 @@
         <v>163</v>
       </c>
       <c r="B175" t="s">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="C175" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D175" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E175" s="17">
         <v>1</v>
@@ -9295,10 +9310,10 @@
         <v>32</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.2">
@@ -9306,13 +9321,13 @@
         <v>164</v>
       </c>
       <c r="B176" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="C176" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D176" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E176" s="18">
         <v>2</v>
@@ -9321,13 +9336,13 @@
         <v>32</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I176" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J176" s="4" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.2">
@@ -9335,13 +9350,13 @@
         <v>165</v>
       </c>
       <c r="B177" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="C177" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D177" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E177" s="19">
         <v>3</v>
@@ -9350,13 +9365,13 @@
         <v>32</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J177" s="4" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.2">
@@ -9364,13 +9379,13 @@
         <v>166</v>
       </c>
       <c r="B178" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="C178" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D178" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E178" s="20">
         <v>4</v>
@@ -9379,13 +9394,13 @@
         <v>32</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J178" s="4" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="L178" s="1"/>
     </row>
@@ -9394,13 +9409,13 @@
         <v>167</v>
       </c>
       <c r="B179" t="s">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="C179" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D179" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E179" s="21">
         <v>5</v>
@@ -9409,16 +9424,16 @@
         <v>32</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H179" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J179" s="4" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="L179" s="1"/>
     </row>
@@ -9427,13 +9442,13 @@
         <v>168</v>
       </c>
       <c r="B180" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="C180" t="s">
-        <v>713</v>
+        <v>704</v>
       </c>
       <c r="D180" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E180" s="17">
         <v>1</v>
@@ -9442,10 +9457,10 @@
         <v>32</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I180" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L180" s="1"/>
     </row>
@@ -9454,13 +9469,13 @@
         <v>169</v>
       </c>
       <c r="B181" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
       <c r="C181" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D181" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E181" s="18">
         <v>2</v>
@@ -9469,13 +9484,13 @@
         <v>32</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I181" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J181" s="4" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="L181" s="1"/>
     </row>
@@ -9484,13 +9499,13 @@
         <v>170</v>
       </c>
       <c r="B182" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="C182" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D182" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E182" s="19">
         <v>3</v>
@@ -9499,13 +9514,13 @@
         <v>32</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I182" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J182" s="4" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="L182" s="1"/>
     </row>
@@ -9514,13 +9529,13 @@
         <v>171</v>
       </c>
       <c r="B183" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="C183" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D183" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E183" s="20">
         <v>4</v>
@@ -9529,13 +9544,13 @@
         <v>32</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I183" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J183" s="4" t="s">
-        <v>667</v>
+        <v>659</v>
       </c>
       <c r="L183" s="1"/>
     </row>
@@ -9544,13 +9559,13 @@
         <v>172</v>
       </c>
       <c r="B184" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="C184" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D184" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E184" s="21">
         <v>5</v>
@@ -9559,16 +9574,16 @@
         <v>32</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H184" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I184" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J184" s="4" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="L184" s="1"/>
     </row>
@@ -9599,28 +9614,28 @@
         <v>176</v>
       </c>
       <c r="B189" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="C189" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D189" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E189" s="17">
         <v>1</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I189" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J189" s="4" t="s">
-        <v>779</v>
+        <v>864</v>
       </c>
     </row>
     <row r="190" spans="1:12" ht="71.25" x14ac:dyDescent="0.2">
@@ -9628,28 +9643,28 @@
         <v>177</v>
       </c>
       <c r="B190" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="C190" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D190" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E190" s="18">
         <v>2</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I190" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J190" s="4" t="s">
-        <v>778</v>
+        <v>865</v>
       </c>
     </row>
     <row r="191" spans="1:12" ht="71.25" x14ac:dyDescent="0.2">
@@ -9657,31 +9672,31 @@
         <v>178</v>
       </c>
       <c r="B191" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
       <c r="C191" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D191" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E191" s="19">
         <v>3</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H191" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I191" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J191" s="4" t="s">
-        <v>780</v>
+        <v>866</v>
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.2">
@@ -9689,13 +9704,13 @@
         <v>179</v>
       </c>
       <c r="B192" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="C192" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D192" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E192" s="17">
         <v>1</v>
@@ -9704,13 +9719,13 @@
         <v>29</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I192" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J192" s="4" t="s">
-        <v>686</v>
+        <v>678</v>
       </c>
     </row>
     <row r="193" spans="1:17" x14ac:dyDescent="0.2">
@@ -9718,13 +9733,13 @@
         <v>180</v>
       </c>
       <c r="B193" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="C193" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D193" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E193" s="18">
         <v>2</v>
@@ -9733,13 +9748,13 @@
         <v>29</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I193" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J193" s="4" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
     </row>
     <row r="194" spans="1:17" x14ac:dyDescent="0.2">
@@ -9747,13 +9762,13 @@
         <v>181</v>
       </c>
       <c r="B194" t="s">
-        <v>680</v>
+        <v>672</v>
       </c>
       <c r="C194" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D194" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E194" s="19">
         <v>3</v>
@@ -9762,16 +9777,16 @@
         <v>29</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H194" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I194" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J194" s="4" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
     </row>
     <row r="195" spans="1:17" x14ac:dyDescent="0.2">
@@ -9779,13 +9794,13 @@
         <v>182</v>
       </c>
       <c r="B195" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="C195" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D195" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E195" s="18">
         <v>2</v>
@@ -9794,13 +9809,13 @@
         <v>35</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I195" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J195" s="4" t="s">
-        <v>688</v>
+        <v>867</v>
       </c>
     </row>
     <row r="196" spans="1:17" x14ac:dyDescent="0.2">
@@ -9808,13 +9823,13 @@
         <v>183</v>
       </c>
       <c r="B196" t="s">
-        <v>682</v>
+        <v>674</v>
       </c>
       <c r="C196" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D196" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E196" s="17">
         <v>1</v>
@@ -9823,16 +9838,16 @@
         <v>27</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I196" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J196" s="4" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
       <c r="K196" s="15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="197" spans="1:17" x14ac:dyDescent="0.2">
@@ -9840,13 +9855,13 @@
         <v>184</v>
       </c>
       <c r="B197" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="C197" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D197" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E197" s="18">
         <v>2</v>
@@ -9855,16 +9870,16 @@
         <v>27</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I197" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J197" s="4" t="s">
-        <v>690</v>
+        <v>681</v>
       </c>
       <c r="K197" s="15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="198" spans="1:17" x14ac:dyDescent="0.2">
@@ -9872,13 +9887,13 @@
         <v>185</v>
       </c>
       <c r="B198" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="C198" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D198" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E198" s="19">
         <v>3</v>
@@ -9887,19 +9902,19 @@
         <v>27</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H198" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I198" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J198" s="4" t="s">
-        <v>691</v>
+        <v>682</v>
       </c>
       <c r="K198" s="15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="199" spans="1:17" x14ac:dyDescent="0.2">
@@ -9920,13 +9935,13 @@
         <v>186</v>
       </c>
       <c r="B200" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C200" t="s">
+        <v>469</v>
+      </c>
+      <c r="D200" t="s">
         <v>470</v>
-      </c>
-      <c r="D200" t="s">
-        <v>471</v>
       </c>
       <c r="E200" s="17">
         <v>1</v>
@@ -9935,10 +9950,10 @@
         <v>35</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I200" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="201" spans="1:17" x14ac:dyDescent="0.2">
@@ -9946,13 +9961,13 @@
         <v>187</v>
       </c>
       <c r="B201" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C201" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D201" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E201" s="18">
         <v>2</v>
@@ -9961,10 +9976,10 @@
         <v>35</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I201" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="202" spans="1:17" x14ac:dyDescent="0.2">
@@ -9972,13 +9987,13 @@
         <v>188</v>
       </c>
       <c r="B202" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C202" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D202" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E202" s="18">
         <v>2</v>
@@ -9987,10 +10002,10 @@
         <v>35</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I202" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="203" spans="1:17" x14ac:dyDescent="0.2">
@@ -9998,13 +10013,13 @@
         <v>189</v>
       </c>
       <c r="B203" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C203" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D203" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E203" s="17">
         <v>1</v>
@@ -10013,10 +10028,10 @@
         <v>35</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I203" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="204" spans="1:17" x14ac:dyDescent="0.2">
@@ -10024,13 +10039,13 @@
         <v>190</v>
       </c>
       <c r="B204" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C204" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D204" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E204" s="17">
         <v>1</v>
@@ -10039,10 +10054,10 @@
         <v>35</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I204" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="205" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.2">
@@ -10063,25 +10078,25 @@
         <v>301</v>
       </c>
       <c r="B206" t="s">
-        <v>784</v>
+        <v>769</v>
       </c>
       <c r="C206" t="s">
-        <v>800</v>
+        <v>785</v>
       </c>
       <c r="D206" t="s">
-        <v>789</v>
+        <v>774</v>
       </c>
       <c r="E206">
         <v>1</v>
       </c>
       <c r="I206" s="1" t="s">
-        <v>782</v>
+        <v>767</v>
       </c>
       <c r="J206" s="4" t="s">
-        <v>786</v>
+        <v>771</v>
       </c>
       <c r="L206" s="15" t="s">
-        <v>787</v>
+        <v>772</v>
       </c>
     </row>
     <row r="207" spans="1:17" ht="28.5" x14ac:dyDescent="0.2">
@@ -10089,25 +10104,25 @@
         <v>302</v>
       </c>
       <c r="B207" t="s">
-        <v>785</v>
+        <v>770</v>
       </c>
       <c r="C207" t="s">
-        <v>801</v>
+        <v>786</v>
       </c>
       <c r="D207" t="s">
-        <v>789</v>
+        <v>774</v>
       </c>
       <c r="E207">
         <v>1</v>
       </c>
       <c r="I207" s="1" t="s">
-        <v>782</v>
+        <v>767</v>
       </c>
       <c r="J207" s="4" t="s">
-        <v>837</v>
+        <v>822</v>
       </c>
       <c r="L207" s="15" t="s">
-        <v>788</v>
+        <v>773</v>
       </c>
     </row>
     <row r="225" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
@@ -10115,22 +10130,22 @@
         <v>320</v>
       </c>
       <c r="B225" t="s">
-        <v>791</v>
+        <v>776</v>
       </c>
       <c r="C225" t="s">
-        <v>796</v>
+        <v>781</v>
       </c>
       <c r="D225" t="s">
-        <v>789</v>
+        <v>774</v>
       </c>
       <c r="E225">
         <v>1</v>
       </c>
       <c r="I225" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J225" s="4" t="s">
-        <v>802</v>
+        <v>787</v>
       </c>
       <c r="L225" s="23">
         <v>401</v>
@@ -10141,22 +10156,22 @@
         <v>321</v>
       </c>
       <c r="B226" t="s">
-        <v>792</v>
+        <v>777</v>
       </c>
       <c r="C226" t="s">
-        <v>797</v>
+        <v>782</v>
       </c>
       <c r="D226" t="s">
-        <v>789</v>
+        <v>774</v>
       </c>
       <c r="E226">
         <v>1</v>
       </c>
       <c r="I226" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J226" s="4" t="s">
-        <v>803</v>
+        <v>788</v>
       </c>
       <c r="L226" s="23">
         <v>401</v>
@@ -10167,22 +10182,22 @@
         <v>322</v>
       </c>
       <c r="B227" t="s">
-        <v>793</v>
+        <v>778</v>
       </c>
       <c r="C227" t="s">
-        <v>798</v>
+        <v>783</v>
       </c>
       <c r="D227" t="s">
-        <v>789</v>
+        <v>774</v>
       </c>
       <c r="E227">
         <v>1</v>
       </c>
       <c r="I227" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J227" s="4" t="s">
-        <v>804</v>
+        <v>789</v>
       </c>
       <c r="L227" s="23">
         <v>402</v>
@@ -10193,22 +10208,22 @@
         <v>323</v>
       </c>
       <c r="B228" t="s">
-        <v>794</v>
+        <v>779</v>
       </c>
       <c r="C228" t="s">
-        <v>799</v>
+        <v>784</v>
       </c>
       <c r="D228" t="s">
-        <v>789</v>
+        <v>774</v>
       </c>
       <c r="E228">
         <v>1</v>
       </c>
       <c r="I228" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J228" s="4" t="s">
-        <v>805</v>
+        <v>790</v>
       </c>
       <c r="L228" s="23">
         <v>402</v>
@@ -10219,22 +10234,22 @@
         <v>324</v>
       </c>
       <c r="B229" t="s">
-        <v>795</v>
+        <v>780</v>
       </c>
       <c r="C229" t="s">
-        <v>807</v>
+        <v>792</v>
       </c>
       <c r="D229" t="s">
-        <v>789</v>
+        <v>774</v>
       </c>
       <c r="E229">
         <v>1</v>
       </c>
       <c r="I229" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J229" s="4" t="s">
-        <v>806</v>
+        <v>791</v>
       </c>
       <c r="L229" s="23">
         <v>403</v>
@@ -10245,22 +10260,22 @@
         <v>325</v>
       </c>
       <c r="B230" t="s">
-        <v>808</v>
+        <v>793</v>
       </c>
       <c r="C230" t="s">
-        <v>828</v>
+        <v>813</v>
       </c>
       <c r="D230" t="s">
-        <v>827</v>
+        <v>812</v>
       </c>
       <c r="E230">
         <v>1</v>
       </c>
       <c r="I230" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J230" s="4" t="s">
-        <v>810</v>
+        <v>795</v>
       </c>
       <c r="L230" s="23">
         <v>407</v>
@@ -10271,22 +10286,22 @@
         <v>326</v>
       </c>
       <c r="B231" t="s">
-        <v>809</v>
+        <v>794</v>
       </c>
       <c r="C231" t="s">
-        <v>829</v>
+        <v>814</v>
       </c>
       <c r="D231" t="s">
-        <v>789</v>
+        <v>774</v>
       </c>
       <c r="E231">
         <v>1</v>
       </c>
       <c r="I231" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J231" s="4" t="s">
-        <v>810</v>
+        <v>795</v>
       </c>
       <c r="L231" s="23">
         <v>408</v>
@@ -10297,22 +10312,22 @@
         <v>327</v>
       </c>
       <c r="B232" t="s">
-        <v>811</v>
+        <v>796</v>
       </c>
       <c r="C232" t="s">
-        <v>830</v>
+        <v>815</v>
       </c>
       <c r="D232" t="s">
-        <v>789</v>
+        <v>774</v>
       </c>
       <c r="E232">
         <v>1</v>
       </c>
       <c r="I232" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J232" s="4" t="s">
-        <v>810</v>
+        <v>795</v>
       </c>
       <c r="L232" s="23">
         <v>409</v>
@@ -10323,22 +10338,22 @@
         <v>328</v>
       </c>
       <c r="B233" t="s">
-        <v>812</v>
+        <v>797</v>
       </c>
       <c r="C233" t="s">
-        <v>831</v>
+        <v>816</v>
       </c>
       <c r="D233" t="s">
-        <v>789</v>
+        <v>774</v>
       </c>
       <c r="E233">
         <v>1</v>
       </c>
       <c r="I233" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J233" s="4" t="s">
-        <v>817</v>
+        <v>802</v>
       </c>
     </row>
     <row r="234" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
@@ -10346,22 +10361,22 @@
         <v>329</v>
       </c>
       <c r="B234" t="s">
-        <v>813</v>
+        <v>798</v>
       </c>
       <c r="C234" t="s">
-        <v>832</v>
+        <v>817</v>
       </c>
       <c r="D234" t="s">
-        <v>789</v>
+        <v>774</v>
       </c>
       <c r="E234">
         <v>1</v>
       </c>
       <c r="I234" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J234" s="4" t="s">
-        <v>817</v>
+        <v>802</v>
       </c>
     </row>
     <row r="235" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
@@ -10369,22 +10384,22 @@
         <v>330</v>
       </c>
       <c r="B235" t="s">
-        <v>814</v>
+        <v>799</v>
       </c>
       <c r="C235" t="s">
-        <v>833</v>
+        <v>818</v>
       </c>
       <c r="D235" t="s">
-        <v>789</v>
+        <v>774</v>
       </c>
       <c r="E235">
         <v>1</v>
       </c>
       <c r="I235" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J235" s="4" t="s">
-        <v>817</v>
+        <v>802</v>
       </c>
     </row>
     <row r="236" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
@@ -10392,22 +10407,22 @@
         <v>331</v>
       </c>
       <c r="B236" t="s">
-        <v>815</v>
+        <v>800</v>
       </c>
       <c r="C236" t="s">
-        <v>834</v>
+        <v>819</v>
       </c>
       <c r="D236" t="s">
-        <v>789</v>
+        <v>774</v>
       </c>
       <c r="E236">
         <v>1</v>
       </c>
       <c r="I236" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J236" s="4" t="s">
-        <v>817</v>
+        <v>802</v>
       </c>
     </row>
     <row r="237" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
@@ -10415,22 +10430,22 @@
         <v>332</v>
       </c>
       <c r="B237" t="s">
-        <v>816</v>
+        <v>801</v>
       </c>
       <c r="C237" t="s">
-        <v>835</v>
+        <v>820</v>
       </c>
       <c r="D237" t="s">
-        <v>789</v>
+        <v>774</v>
       </c>
       <c r="E237">
         <v>1</v>
       </c>
       <c r="I237" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J237" s="4" t="s">
-        <v>817</v>
+        <v>802</v>
       </c>
     </row>
     <row r="238" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
@@ -10438,22 +10453,22 @@
         <v>333</v>
       </c>
       <c r="B238" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="C238" t="s">
-        <v>818</v>
+        <v>803</v>
       </c>
       <c r="D238" t="s">
-        <v>789</v>
+        <v>774</v>
       </c>
       <c r="E238">
         <v>1</v>
       </c>
       <c r="I238" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J238" s="4" t="s">
-        <v>824</v>
+        <v>809</v>
       </c>
       <c r="L238" s="23">
         <v>404</v>
@@ -10464,22 +10479,22 @@
         <v>334</v>
       </c>
       <c r="B239" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
       <c r="C239" t="s">
-        <v>819</v>
+        <v>804</v>
       </c>
       <c r="D239" t="s">
-        <v>789</v>
+        <v>774</v>
       </c>
       <c r="E239">
         <v>1</v>
       </c>
       <c r="I239" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J239" s="4" t="s">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="L239" s="23">
         <v>405</v>
@@ -10490,22 +10505,22 @@
         <v>335</v>
       </c>
       <c r="B240" t="s">
-        <v>823</v>
+        <v>808</v>
       </c>
       <c r="C240" t="s">
-        <v>820</v>
+        <v>805</v>
       </c>
       <c r="D240" t="s">
-        <v>789</v>
+        <v>774</v>
       </c>
       <c r="E240">
         <v>1</v>
       </c>
       <c r="I240" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J240" s="4" t="s">
-        <v>826</v>
+        <v>811</v>
       </c>
       <c r="L240" s="23">
         <v>406</v>
@@ -10538,20 +10553,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{951DF8F7-72B0-488B-B4D5-B6A179D17BB0}">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="35.875" customWidth="1"/>
     <col min="3" max="3" width="18.625" customWidth="1"/>
-    <col min="4" max="4" width="27.625" customWidth="1"/>
-    <col min="5" max="5" width="21.875" style="4" customWidth="1"/>
-    <col min="6" max="6" width="25.25" style="4" customWidth="1"/>
-    <col min="7" max="7" width="27.5" style="4" customWidth="1"/>
-    <col min="8" max="8" width="32.625" customWidth="1"/>
-    <col min="9" max="9" width="29.75" customWidth="1"/>
+    <col min="4" max="5" width="27.625" customWidth="1"/>
+    <col min="6" max="6" width="21.875" style="4" customWidth="1"/>
+    <col min="7" max="7" width="25.25" style="4" customWidth="1"/>
+    <col min="8" max="8" width="27.5" style="4" customWidth="1"/>
+    <col min="9" max="9" width="32.625" customWidth="1"/>
+    <col min="10" max="10" width="29.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" t="s">
         <v>0</v>
@@ -10560,25 +10575,28 @@
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>857</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>199</v>
+        <v>842</v>
+      </c>
+      <c r="E1" t="s">
+        <v>847</v>
       </c>
       <c r="F1" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
+        <v>205</v>
+      </c>
+      <c r="J1" t="s">
         <v>206</v>
       </c>
-      <c r="I1" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -10591,23 +10609,26 @@
       <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>198</v>
+      <c r="E2" t="s">
+        <v>848</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="G2" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="I2" t="s">
         <v>203</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>204</v>
       </c>
-      <c r="I2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -10620,439 +10641,458 @@
       <c r="D3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" t="s">
+        <v>849</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>79</v>
-      </c>
       <c r="G3" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="H3" t="s">
-        <v>208</v>
+        <v>78</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>78</v>
       </c>
       <c r="I3" t="s">
-        <v>208</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+        <v>207</v>
+      </c>
+      <c r="J3" t="s">
+        <v>207</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1000</v>
       </c>
       <c r="B4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D4" t="s">
-        <v>861</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="H4" t="b">
+        <v>846</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="I4" t="b">
         <v>1</v>
       </c>
-      <c r="I4" t="b">
+      <c r="J4" t="b">
         <v>0</v>
       </c>
-      <c r="L4" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M4" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1001</v>
       </c>
       <c r="B5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D5" t="s">
-        <v>861</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
+        <v>846</v>
+      </c>
+      <c r="E5" t="s">
+        <v>850</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>86</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
       </c>
-      <c r="L5" s="1" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1002</v>
       </c>
       <c r="B6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D6" t="s">
-        <v>861</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
+        <v>846</v>
+      </c>
+      <c r="E6" t="s">
+        <v>851</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>225</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
       </c>
-      <c r="L6" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>1003</v>
       </c>
       <c r="B7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D7" t="s">
-        <v>861</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="H7" t="b">
-        <v>0</v>
+        <v>846</v>
+      </c>
+      <c r="E7" t="s">
+        <v>851</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>226</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
       </c>
-      <c r="L7" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1004</v>
       </c>
       <c r="B8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D8" t="s">
-        <v>861</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
+        <v>846</v>
+      </c>
+      <c r="E8" t="s">
+        <v>851</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>228</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
       </c>
-      <c r="L8" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>1005</v>
       </c>
       <c r="B9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D9" t="s">
-        <v>861</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="H9" t="b">
-        <v>0</v>
+        <v>846</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>230</v>
       </c>
       <c r="I9" t="b">
         <v>0</v>
       </c>
-      <c r="L9" s="1" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>1006</v>
       </c>
       <c r="B10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D10" t="s">
-        <v>861</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
+        <v>846</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="I10" t="b">
         <v>0</v>
       </c>
-      <c r="L10" s="1" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>1007</v>
       </c>
       <c r="B11" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C11" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D11" t="s">
-        <v>861</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F11" s="4">
+        <v>846</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="G11" s="4">
         <v>1006</v>
-      </c>
-      <c r="H11" t="b">
-        <v>0</v>
       </c>
       <c r="I11" t="b">
         <v>0</v>
       </c>
-      <c r="L11" s="1" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>1008</v>
       </c>
       <c r="B12" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C12" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D12" t="s">
-        <v>861</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="H12" t="b">
-        <v>0</v>
+        <v>846</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>224</v>
       </c>
       <c r="I12" t="b">
         <v>0</v>
       </c>
-      <c r="L12" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>1009</v>
       </c>
       <c r="B13" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D13" t="s">
-        <v>861</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="H13" t="b">
-        <v>0</v>
+        <v>846</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>186</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
       </c>
-      <c r="L13" s="1" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>1010</v>
       </c>
       <c r="B14" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C14" t="s">
+        <v>216</v>
+      </c>
+      <c r="D14" t="s">
+        <v>846</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>217</v>
-      </c>
-      <c r="D14" t="s">
-        <v>861</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="H14" t="b">
-        <v>0</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>
       </c>
-      <c r="L14" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>1011</v>
       </c>
       <c r="B15" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C15" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D15" t="s">
-        <v>861</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="H15" t="b">
-        <v>0</v>
+        <v>846</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>233</v>
       </c>
       <c r="I15" t="b">
         <v>0</v>
       </c>
-      <c r="L15" s="1"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>1012</v>
       </c>
       <c r="B16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D16" t="s">
-        <v>861</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="F16">
+        <v>846</v>
+      </c>
+      <c r="E16" t="s">
+        <v>852</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="G16">
         <v>1005</v>
-      </c>
-      <c r="H16" t="b">
-        <v>0</v>
       </c>
       <c r="I16" t="b">
         <v>0</v>
       </c>
-      <c r="L16" s="1"/>
-    </row>
-    <row r="17" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1"/>
+    </row>
+    <row r="17" spans="1:13" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>1013</v>
       </c>
       <c r="B17" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C17" t="s">
+        <v>231</v>
+      </c>
+      <c r="D17" t="s">
+        <v>846</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="D17" t="s">
-        <v>861</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="F17"/>
-      <c r="H17" t="b">
-        <v>0</v>
-      </c>
+      <c r="G17"/>
       <c r="I17" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>1014</v>
       </c>
       <c r="B18" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C18" t="s">
+        <v>264</v>
+      </c>
+      <c r="D18" t="s">
+        <v>846</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>265</v>
-      </c>
-      <c r="D18" t="s">
-        <v>861</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="H18" t="b">
-        <v>0</v>
       </c>
       <c r="I18" t="b">
         <v>0</v>
       </c>
-      <c r="L18" s="1"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="M18" s="1"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>1015</v>
       </c>
       <c r="B19" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C19" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D19" t="s">
-        <v>861</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="H19" t="b">
+        <v>846</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="I19" t="b">
         <v>0</v>
       </c>
-      <c r="I19" t="b">
+      <c r="J19" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -11077,18 +11117,18 @@
         <v>0</v>
       </c>
       <c r="E1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
         <v>17</v>
@@ -11097,10 +11137,10 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -11131,16 +11171,16 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
+        <v>142</v>
+      </c>
+      <c r="D4" t="s">
         <v>143</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>144</v>
       </c>
-      <c r="E4" t="s">
-        <v>145</v>
-      </c>
       <c r="F4" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -11151,16 +11191,16 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D5" t="s">
         <v>143</v>
       </c>
-      <c r="D5" t="s">
-        <v>144</v>
-      </c>
       <c r="E5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -11171,16 +11211,16 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
+        <v>142</v>
+      </c>
+      <c r="D6" t="s">
         <v>143</v>
       </c>
-      <c r="D6" t="s">
-        <v>144</v>
-      </c>
       <c r="E6" t="s">
+        <v>146</v>
+      </c>
+      <c r="F6" s="9" t="s">
         <v>147</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -11191,16 +11231,16 @@
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -11213,16 +11253,16 @@
         <v>2</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -11235,16 +11275,16 @@
         <v>3</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -11257,16 +11297,16 @@
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -11279,16 +11319,16 @@
         <v>2</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -11301,16 +11341,16 @@
         <v>3</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -11323,16 +11363,16 @@
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -11345,16 +11385,16 @@
         <v>2</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
@@ -11365,16 +11405,16 @@
         <v>3</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
@@ -11385,16 +11425,16 @@
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E16" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
@@ -11405,16 +11445,16 @@
         <v>2</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
@@ -11425,16 +11465,16 @@
         <v>3</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E18" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
@@ -11445,16 +11485,16 @@
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
@@ -11465,16 +11505,16 @@
         <v>2</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E20" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
@@ -11485,16 +11525,16 @@
         <v>3</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
@@ -11505,16 +11545,16 @@
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E22" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
@@ -11525,16 +11565,16 @@
         <v>2</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
@@ -11545,16 +11585,16 @@
         <v>3</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E24" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
@@ -11596,7 +11636,7 @@
         <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>11</v>
@@ -11616,7 +11656,7 @@
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>18</v>
@@ -11653,19 +11693,19 @@
         <v>20</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>859</v>
+        <v>844</v>
       </c>
       <c r="D4" t="s">
-        <v>838</v>
+        <v>823</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>722</v>
+        <v>713</v>
       </c>
       <c r="O4" t="s">
-        <v>839</v>
+        <v>824</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
@@ -11676,19 +11716,19 @@
         <v>21</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>859</v>
+        <v>844</v>
       </c>
       <c r="D5" t="s">
-        <v>838</v>
+        <v>823</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>723</v>
+        <v>714</v>
       </c>
       <c r="O5" t="s">
-        <v>841</v>
+        <v>826</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
@@ -11699,16 +11739,16 @@
         <v>22</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>859</v>
+        <v>844</v>
       </c>
       <c r="D6" t="s">
-        <v>838</v>
+        <v>823</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>724</v>
+        <v>715</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
@@ -11719,16 +11759,16 @@
         <v>34</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>859</v>
+        <v>844</v>
       </c>
       <c r="D7" t="s">
-        <v>838</v>
+        <v>823</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>725</v>
+        <v>716</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
@@ -11739,16 +11779,16 @@
         <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>859</v>
+        <v>844</v>
       </c>
       <c r="D8" t="s">
-        <v>838</v>
+        <v>823</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>726</v>
+        <v>717</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
@@ -11759,16 +11799,16 @@
         <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>859</v>
+        <v>844</v>
       </c>
       <c r="D9" t="s">
-        <v>838</v>
+        <v>823</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>727</v>
+        <v>718</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
@@ -11779,16 +11819,16 @@
         <v>24</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>859</v>
+        <v>844</v>
       </c>
       <c r="D10" t="s">
-        <v>838</v>
+        <v>823</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>728</v>
+        <v>719</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
@@ -11797,62 +11837,62 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>860</v>
+        <v>845</v>
       </c>
       <c r="D12" t="s">
-        <v>840</v>
+        <v>825</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>729</v>
+        <v>720</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>293</v>
-      </c>
       <c r="C13" s="1" t="s">
-        <v>860</v>
+        <v>845</v>
       </c>
       <c r="D13" t="s">
-        <v>840</v>
+        <v>825</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>730</v>
+        <v>721</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>860</v>
+        <v>845</v>
       </c>
       <c r="D14" t="s">
-        <v>840</v>
+        <v>825</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>731</v>
+        <v>722</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
@@ -11863,96 +11903,96 @@
         <v>26</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>860</v>
+        <v>845</v>
       </c>
       <c r="D15" t="s">
-        <v>840</v>
+        <v>825</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>732</v>
+        <v>723</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>287</v>
-      </c>
       <c r="C16" s="1" t="s">
-        <v>860</v>
+        <v>845</v>
       </c>
       <c r="D16" t="s">
-        <v>840</v>
+        <v>825</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>733</v>
+        <v>724</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>290</v>
-      </c>
       <c r="C17" s="1" t="s">
-        <v>860</v>
+        <v>845</v>
       </c>
       <c r="D17" t="s">
-        <v>840</v>
+        <v>825</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>296</v>
-      </c>
       <c r="C18" s="1" t="s">
-        <v>860</v>
+        <v>845</v>
       </c>
       <c r="D18" t="s">
-        <v>840</v>
+        <v>825</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>735</v>
+        <v>726</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>299</v>
-      </c>
       <c r="C19" s="1" t="s">
-        <v>860</v>
+        <v>845</v>
       </c>
       <c r="D19" t="s">
-        <v>840</v>
+        <v>825</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>736</v>
+        <v>727</v>
       </c>
     </row>
   </sheetData>
@@ -11980,13 +12020,13 @@
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" t="s">
-        <v>856</v>
+        <v>841</v>
       </c>
       <c r="C1" t="s">
         <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>737</v>
+        <v>728</v>
       </c>
       <c r="E1" s="1"/>
     </row>
@@ -11995,7 +12035,7 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>855</v>
+        <v>840</v>
       </c>
       <c r="C2" t="s">
         <v>10</v>
@@ -12016,18 +12056,18 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>741</v>
+        <v>732</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>842</v>
+        <v>827</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>858</v>
+        <v>843</v>
       </c>
       <c r="D4">
         <v>0.6</v>
@@ -12035,13 +12075,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>828</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>843</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>858</v>
       </c>
       <c r="D5">
         <v>0.8</v>
@@ -12049,13 +12089,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>844</v>
+        <v>829</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>858</v>
+        <v>843</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -12063,13 +12103,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>845</v>
+        <v>830</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>858</v>
+        <v>843</v>
       </c>
       <c r="D7">
         <v>1.5</v>
@@ -12077,13 +12117,13 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>846</v>
+        <v>831</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>858</v>
+        <v>843</v>
       </c>
       <c r="D8">
         <v>0.8</v>
@@ -12091,13 +12131,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>847</v>
+        <v>832</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>858</v>
+        <v>843</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -12105,13 +12145,13 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>853</v>
+        <v>838</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>858</v>
+        <v>843</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -12119,13 +12159,13 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>849</v>
+        <v>834</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>858</v>
+        <v>843</v>
       </c>
       <c r="D11">
         <v>0.6</v>
@@ -12133,13 +12173,13 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>850</v>
+        <v>835</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>858</v>
+        <v>843</v>
       </c>
       <c r="D12">
         <v>0.5</v>
@@ -12147,13 +12187,13 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>851</v>
+        <v>836</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>858</v>
+        <v>843</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -12161,13 +12201,13 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>852</v>
+        <v>837</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>858</v>
+        <v>843</v>
       </c>
       <c r="D14">
         <v>1.2</v>
@@ -12175,13 +12215,13 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>848</v>
+        <v>833</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>858</v>
+        <v>843</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -12189,13 +12229,13 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>827</v>
+        <v>812</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>854</v>
+        <v>839</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>858</v>
+        <v>843</v>
       </c>
       <c r="D16">
         <v>3</v>
@@ -12218,21 +12258,21 @@
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" t="s">
-        <v>737</v>
+        <v>728</v>
       </c>
       <c r="C1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -12254,7 +12294,7 @@
         <v>10</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -12265,7 +12305,7 @@
         <v>30</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -12276,7 +12316,7 @@
         <v>50</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -12287,7 +12327,7 @@
         <v>80</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>740</v>
+        <v>731</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -12298,7 +12338,7 @@
         <v>120</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
